--- a/Report_Template.xlsx
+++ b/Report_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cheukon_yau\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04AC14FE-1452-49A9-88D8-31E6ECA5E3CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E92B3FEC-93D1-43BF-8B08-FFF8CD8646FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D41072CE-D920-4571-B672-638BFC26A6EF}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Data" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RP!$A$1:$J$51</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RP!$A$1:$V$51</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
   <si>
     <t>Reprot</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -72,7 +72,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>rev1</t>
+    <t>Results:</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rev2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -457,15 +461,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15D0DF16-5012-4323-A8FD-775510B16344}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="22" width="3.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -497,9 +504,18 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <f>IFERROR(B5-B4,"N/A")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>7</v>
       </c>
-      <c r="B7">
+      <c r="B10">
         <f>Data!A2</f>
         <v>0</v>
       </c>
